--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -716,16 +716,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>2.2</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -802,16 +820,34 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>-6.7</v>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -870,16 +906,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-6.2</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -887,16 +941,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>0.099</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1006,16 +1078,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>40.469</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BCEAO</t>
+          <t>BCEAO Monetary Policy Committee communiqué</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANSD</t>
+          <t>ANSD, Bulletin Mensuel des Prix à la Consommation Août 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -731,19 +731,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>ANSD / IMF</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -778,7 +774,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>end-2024</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -788,12 +784,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Feb-25</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>revised after audit of unrecorded borrowing (previously ~74%)</t>
+          <t>Public sector debt, as reconciled by Cour des Comptes audit with IMF technical assistance (previously reported ~74%)</t>
         </is>
       </c>
     </row>
@@ -1113,15 +1109,29 @@
           <t>eurobonds_outstanding_usd_bn</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ministry of Finance, Stratégie de Dette à Moyen Terme et Exécution Budgétaire 2026 (approx. USD equivalent of EUR 500M 2028, USD 500M 2031, USD 1.1B 2033, EUR 1.0B 2037, USD 1.0B 2048)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1256,7 +1266,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
+          <t>Successor financing arrangement (staff-level agreement) replacing suspended EFF/ECF approved Jun-23</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1279,7 +1289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1293,10 +1303,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1309,7 +1334,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1318,7 +1346,18 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ANSD / IMF, Sep-26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1327,7 +1366,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1336,7 +1378,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1345,7 +1390,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1354,7 +1402,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1363,9 +1414,18 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cour des Comptes / IMF, Sep-26 (public sector debt, reconciled)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1374,7 +1434,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1383,7 +1446,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1392,7 +1458,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1401,7 +1470,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -647,12 +647,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BCEAO Monetary Policy Committee communiqué</t>
+          <t>BCEAO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANSD, Bulletin Mensuel des Prix à la Consommation Août 2026</t>
+          <t>ANSD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Public sector debt, as reconciled by Cour des Comptes audit with IMF technical assistance (previously reported ~74%)</t>
+          <t>Public debt, ~132% of GDP at end-2024 against ~74% previously reported; attribution (Cour des Comptes Feb-25 vs later IMF reconciliation) unresolved</t>
         </is>
       </c>
     </row>
@@ -839,11 +839,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -925,11 +921,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1097,11 +1089,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1266,7 +1254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Successor financing arrangement (staff-level agreement) replacing suspended EFF/ECF approved Jun-23</t>
+          <t>Staff-level agreement on new arrangement replacing suspended $1.8B facility</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1274,7 +1262,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15-Dec-26 (Executive Board consideration)</t>
+          <t>Executive Board consideration 15-Dec-26</t>
         </is>
       </c>
     </row>
@@ -1336,8 +1324,14 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" s="2" t="n">
+        <v>40.469</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>IMF WEO, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1355,7 +1349,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANSD / IMF, Sep-26</t>
+          <t>ANSD / IMF, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1380,8 +1374,14 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" s="2" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IMF WEO, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1392,8 +1392,14 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" s="2" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>IMF WEO, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1423,7 +1429,7 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cour des Comptes / IMF, Sep-26 (public sector debt, reconciled)</t>
+          <t>Cour des Comptes / IMF, 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/senegal.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/senegal.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ANSD / IMF</t>
+          <t>ANSD / IMF WEO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Public debt, ~132% of GDP at end-2024 against ~74% previously reported; attribution (Cour des Comptes Feb-25 vs later IMF reconciliation) unresolved</t>
+          <t>Public debt after hidden-borrowing revaluation; attribution (Cour des Comptes Feb-25 vs later IMF reconciliation) unresolved</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Staff-level agreement on new arrangement replacing suspended $1.8B facility</t>
+          <t>New arrangement (staff-level agreement) replacing the suspended USD 1.8bn facility</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Executive Board consideration 15-Dec-26</t>
+          <t>Board consideration 15-Dec-26</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANSD / IMF, 08-Oct-26</t>
+          <t>ANSD / IMF WEO, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cour des Comptes / IMF, 08-Oct-26</t>
+          <t>Cour des Comptes / IMF, 08-Oct-26 (attribution unresolved)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Public debt after hidden-borrowing revaluation; attribution (Cour des Comptes Feb-25 vs later IMF reconciliation) unresolved</t>
+          <t>Public debt, end-2024 (approx.; attribution to Cour des Comptes vs later IMF reconciliation unresolved)</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New arrangement (staff-level agreement) replacing the suspended USD 1.8bn facility</t>
+          <t>Staff-level agreement on new arrangement replacing suspended facility; Board consideration 15-Dec-26</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Board consideration 15-Dec-26</t>
+          <t>15-Dec-26 (Executive Board consideration)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANSD / IMF WEO, 08-Oct-26</t>
+          <t>IMF WEO, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cour des Comptes / IMF, 08-Oct-26 (attribution unresolved)</t>
+          <t>Cour des Comptes / IMF, 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BCEAO</t>
+          <t>BCEAO (marginal lending rate 5.0%)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cour des Comptes / IMF</t>
+          <t>Cour des Comptes / IMF (via data record)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Public debt, end-2024 (approx.; attribution to Cour des Comptes vs later IMF reconciliation unresolved)</t>
+          <t>Public debt, about 132% of GDP at end-2024 after hidden-borrowing revisions (previously reported about 74%); attribution to Cour des Comptes Feb-25 vs later IMF reconciliation unresolved</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Staff-level agreement on new arrangement replacing suspended facility; Board consideration 15-Dec-26</t>
+          <t>Staff-level agreement on new arrangement replacing suspended USD 1.8B facility; Board consideration 15-Dec-26</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IMF WEO, 08-Oct-26</t>
+          <t>ANSD / IMF WEO, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cour des Comptes / IMF, 08-Oct-26</t>
+          <t>Cour des Comptes / IMF (attribution unresolved), 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BCEAO (marginal lending rate 5.0%)</t>
+          <t>BCEAO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Public debt, about 132% of GDP at end-2024 after hidden-borrowing revisions (previously reported about 74%); attribution to Cour des Comptes Feb-25 vs later IMF reconciliation unresolved</t>
+          <t>Public debt after hidden-borrowing revisions; attribution to Cour des Comptes (Feb-25) vs later IMF reconciliation unresolved</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>40.469</v>
+        <v>40.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Staff-level agreement on new arrangement replacing suspended USD 1.8B facility; Board consideration 15-Dec-26</t>
+          <t>Staff-level agreement on new arrangement replacing the suspended USD 1.8bn facility</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1325,7 +1325,7 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n">
-        <v>40.469</v>
+        <v>40.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cour des Comptes / IMF (attribution unresolved), 08-Oct-26</t>
+          <t>Cour des Comptes / IMF, 08-Oct-26 (attribution unresolved)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cour des Comptes / IMF (via data record)</t>
+          <t>Cour des Comptes / IMF (via knowledge page)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Public debt after hidden-borrowing revisions; attribution to Cour des Comptes (Feb-25) vs later IMF reconciliation unresolved</t>
+          <t>Public debt, approximate; attribution to Cour des Comptes (Feb-25) versus later IMF/authorities reconciliation unresolved</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>40.5</v>
+        <v>40.469</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Staff-level agreement on new arrangement replacing the suspended USD 1.8bn facility</t>
+          <t>USD 2.2bn arrangement, staff-level agreement Sep-26, replacing suspended USD 1.8bn facility</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15-Dec-26 (Executive Board consideration)</t>
+          <t>Executive Board consideration 15-Dec-26</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n">
-        <v>40.5</v>
+        <v>40.469</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cour des Comptes / IMF, 08-Oct-26 (attribution unresolved)</t>
+          <t>Cour des Comptes / IMF via knowledge page, 08-Oct-26 (attribution unresolved)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/senegal.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/senegal.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/senegal.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/senegal.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Senegal_Sovereign_Model.xlsx
+++ b/models/sovereigns/Senegal_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/senegal.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/senegal.json</t>
         </is>
       </c>
     </row>
